--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/listAdmins-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/listAdmins-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
-  <si>
-    <t>Statement: UserService.listAdmins(options?) – Delegates to userRepository.findAdmins(options). Supports optional search/pagination options.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="42">
+  <si>
+    <t>Statement: UserService.listAdmins(options)</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: AdminListOptions? { search?, page?, pageSize? }</t>
+    <t>Input: AdminListOptions</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>userRepository is accessible</t>
+    <t>userRepository accessible</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;PageResult&lt;AdminWithUser&gt;&gt;</t>
+    <t>Output: PageResult</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Returns paginated page of admins.</t>
+    <t>Admins page returned.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,24 +64,6 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>no options</t>
-  </si>
-  <si>
-    <t>passes undefined to repo, returns page</t>
-  </si>
-  <si>
-    <t>with options</t>
-  </si>
-  <si>
-    <t>options passed through to repo</t>
-  </si>
-  <si>
-    <t>empty DB</t>
-  </si>
-  <si>
-    <t>items=[], total=0</t>
-  </si>
-  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -97,79 +79,28 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>no options, repo returns 1 admin</t>
-  </si>
-  <si>
-    <t>items.length=1; findAdmins(undefined) called</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>{ search: "Admin", page: 1, pageSize: 10 }</t>
-  </si>
-  <si>
-    <t>findAdmins called with those options</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>no options, repo returns empty</t>
-  </si>
-  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>empty result</t>
-  </si>
-  <si>
-    <t>No admins in repo → total=0</t>
-  </si>
-  <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>empty</t>
-  </si>
-  <si>
-    <t>Empty repo</t>
-  </si>
-  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>No options, 1 admin</t>
-  </si>
-  <si>
-    <t>items.length=1</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>With search options</t>
-  </si>
-  <si>
-    <t>findAdmins(options) called</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>BVA-1</t>
+    <t>List admins</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>Testing</t>
@@ -727,7 +658,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -749,48 +680,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -799,7 +688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -811,70 +700,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -885,7 +723,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -895,24 +733,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +750,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -935,36 +762,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -975,7 +785,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -988,22 +798,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1011,19 +821,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1031,19 +841,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1051,19 +861,239 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>20</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1091,16 +1121,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1108,45 +1138,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1155,19 +1185,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/listAdmins-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/listAdmins-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="42">
-  <si>
-    <t>Statement: UserService.listAdmins(options)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="82">
+  <si>
+    <t>Statement: UserService.listAdmins(options) – Returns a paginated list of admins. Supports optional filtering by search term, pagination by page number and page size. Results are ordered by fullName ascending. Returns an empty list when no admins exist.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: AdminListOptions</t>
+    <t>Input: AdminListOptions { search?: string, page?: number, pageSize?: number }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>userRepository accessible</t>
+    <t>Admins may or may not exist in the system. All options fields are optional.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: PageResult</t>
+    <t>Output: PageResult&lt;AdminWithUser&gt; { items: AdminWithUser[], total: number }</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Admins page returned.</t>
+    <t>On success: items and total returned matching the provided options. Items ordered by fullName ascending.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,6 +64,24 @@
     <t>Invalid EC</t>
   </si>
   <si>
+    <t>Search filter</t>
+  </si>
+  <si>
+    <t>Search term provided → filtered results returned</t>
+  </si>
+  <si>
+    <t>No options provided → default page returned</t>
+  </si>
+  <si>
+    <t>Data availability</t>
+  </si>
+  <si>
+    <t>Multiple admins exist → ordered list returned</t>
+  </si>
+  <si>
+    <t>Empty database → empty list, total: 0</t>
+  </si>
+  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -79,30 +97,132 @@
     <t>Actual Result</t>
   </si>
   <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>No options</t>
+  </si>
+  <si>
+    <t>PageResult returned with items and total</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>search: "Admin"</t>
+  </si>
+  <si>
+    <t>PageResult returned with matching items and total</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>DB contains "Alice" and "John Doe"</t>
+  </si>
+  <si>
+    <t>PageResult returned with "Alice" at index 0, "John Doe" at index 1, total: 2</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>Empty DB</t>
+  </si>
+  <si>
+    <t>PageResult returned with no items and total: 0</t>
+  </si>
+  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
+    <t>Search term length</t>
+  </si>
+  <si>
+    <t>undefined, "" (empty), "a" (1 char)</t>
+  </si>
+  <si>
+    <t>Page number</t>
+  </si>
+  <si>
+    <t>undefined, 0 (treated as page 1), 1 (first page), 2 (second page)</t>
+  </si>
+  <si>
+    <t>Page size</t>
+  </si>
+  <si>
+    <t>undefined (default size), 0 (no items), 1 (one item)</t>
+  </si>
+  <si>
     <t>BVA</t>
   </si>
   <si>
+    <t>BVA-1</t>
+  </si>
+  <si>
+    <t>search: undefined</t>
+  </si>
+  <si>
+    <t>search: ""</t>
+  </si>
+  <si>
+    <t>search: "a"</t>
+  </si>
+  <si>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>page: undefined</t>
+  </si>
+  <si>
+    <t>PageResult returned - page 1 items and total</t>
+  </si>
+  <si>
+    <t>page: 0</t>
+  </si>
+  <si>
+    <t>page: 1</t>
+  </si>
+  <si>
+    <t>page: 2</t>
+  </si>
+  <si>
+    <t>PageResult returned - page 2 is empty, total reflects full count</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>pageSize: undefined</t>
+  </si>
+  <si>
+    <t>PageResult returned with default page size applied</t>
+  </si>
+  <si>
+    <t>pageSize: 0</t>
+  </si>
+  <si>
+    <t>PageResult returned with no items on page, total reflects full count</t>
+  </si>
+  <si>
+    <t>pageSize: 1</t>
+  </si>
+  <si>
+    <t>PageResult returned with exactly 1 item on page, total reflects full count</t>
+  </si>
+  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>List admins</t>
-  </si>
-  <si>
-    <t>Success</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -133,7 +253,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>AUTH-06</t>
+    <t>SERV-08</t>
   </si>
   <si>
     <t>n/a</t>
@@ -658,7 +778,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -680,6 +800,62 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -688,7 +864,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -700,19 +876,87 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +967,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -733,13 +977,46 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -750,7 +1027,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -762,19 +1039,189 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -798,22 +1245,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -821,19 +1268,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -841,19 +1288,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,19 +1308,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -881,19 +1328,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -901,19 +1348,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -921,19 +1368,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -941,19 +1388,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -961,19 +1408,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -981,19 +1428,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1001,19 +1448,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1021,19 +1468,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1041,19 +1488,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1061,19 +1508,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1081,19 +1528,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1121,16 +1568,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1138,39 +1585,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="B3" s="1">
         <v>14</v>
@@ -1185,19 +1632,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/listAdmins-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/listAdmins-bbt-form.xlsx
@@ -253,7 +253,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SERV-08</t>
+    <t>SERV-09</t>
   </si>
   <si>
     <t>n/a</t>
